--- a/data-ingestion-processing/ingestionData/incoming/spreadsheet.xlsx
+++ b/data-ingestion-processing/ingestionData/incoming/spreadsheet.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Status" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="120">
   <si>
     <t xml:space="preserve">Sr. No.</t>
   </si>
@@ -285,6 +286,102 @@
   </si>
   <si>
     <t xml:space="preserve">BEDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File Ingestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-format support pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read file content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chunking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using TokenTextSplitter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedding generation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-modal embeddings pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector database storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metadata extraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document &amp; Chunk metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error handling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File validation &amp; exception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document versioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG citations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response reference in data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text cleaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headers/footers, page breaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document &amp; Chunk ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Id for both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checksum/duplicate detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batch ingestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reranking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check scope of this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reindexing</t>
   </si>
 </sst>
 </file>
@@ -294,7 +391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -335,6 +432,28 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -379,7 +498,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -402,6 +521,34 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -532,11 +679,11 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -547,7 +694,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -558,7 +705,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -569,7 +716,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -580,7 +727,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -591,7 +738,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -602,7 +749,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -613,7 +760,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -624,7 +771,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -635,7 +782,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -646,7 +793,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -657,7 +804,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -668,7 +815,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -679,7 +826,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -690,7 +837,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -701,7 +848,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -712,7 +859,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -723,7 +870,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -734,7 +881,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -745,7 +892,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -756,7 +903,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -767,7 +914,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -778,7 +925,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -789,7 +936,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -800,7 +947,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -811,7 +958,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -822,7 +969,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -833,7 +980,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -844,7 +991,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -855,7 +1002,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -866,7 +1013,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -877,7 +1024,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -888,7 +1035,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -899,7 +1046,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="1" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -910,7 +1057,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+      <c r="A35" s="1" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -921,7 +1068,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -932,7 +1079,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -943,7 +1090,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -954,7 +1101,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="1" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -965,7 +1112,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="1" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -976,7 +1123,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="1" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -987,7 +1134,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+      <c r="A42" s="1" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -998,7 +1145,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+      <c r="A43" s="1" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -1009,7 +1156,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+      <c r="A44" s="1" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -1020,7 +1167,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="A45" s="1" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -1031,7 +1178,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+      <c r="A46" s="1" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -1042,7 +1189,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+      <c r="A47" s="1" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -1053,7 +1200,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="A48" s="1" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -1064,7 +1211,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+      <c r="A49" s="1" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -1075,7 +1222,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+      <c r="A50" s="1" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -1086,7 +1233,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="A51" s="1" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -1097,7 +1244,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+      <c r="A52" s="1" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -1108,7 +1255,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="n">
+      <c r="A53" s="1" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -1119,7 +1266,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
+      <c r="A54" s="1" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -1130,7 +1277,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="n">
+      <c r="A55" s="1" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -1141,7 +1288,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="n">
+      <c r="A56" s="1" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -1175,12 +1322,12 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -1191,7 +1338,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1202,7 +1349,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1213,7 +1360,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1224,7 +1371,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1235,7 +1382,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1246,7 +1393,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1257,7 +1404,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1268,7 +1415,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1279,7 +1426,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1290,7 +1437,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1301,7 +1448,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1312,7 +1459,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1323,7 +1470,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1334,7 +1481,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1345,7 +1492,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1356,7 +1503,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1367,7 +1514,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1378,7 +1525,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1389,7 +1536,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1400,7 +1547,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1411,7 +1558,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1422,7 +1569,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1433,7 +1580,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -1444,7 +1591,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -1455,7 +1602,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -1466,7 +1613,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -1477,7 +1624,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1486,6 +1633,301 @@
       <c r="C28" s="2" t="s">
         <v>61</v>
       </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28.94"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/data-ingestion-processing/ingestionData/incoming/spreadsheet.xlsx
+++ b/data-ingestion-processing/ingestionData/incoming/spreadsheet.xlsx
@@ -348,10 +348,10 @@
     <t xml:space="preserve">Document versioning</t>
   </si>
   <si>
+    <t xml:space="preserve">RAG citations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAG citations</t>
   </si>
   <si>
     <t xml:space="preserve">Response reference in data</t>
@@ -436,7 +436,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFF860D"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -560,6 +560,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF860D"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1773,7 +1833,7 @@
         <v>107</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D9" s="10"/>
     </row>
@@ -1782,10 +1842,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>109</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>108</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>110</v>
@@ -1799,7 +1859,7 @@
         <v>111</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>112</v>
@@ -1813,7 +1873,7 @@
         <v>113</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>114</v>
@@ -1827,7 +1887,7 @@
         <v>115</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1838,7 +1898,7 @@
         <v>116</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/data-ingestion-processing/ingestionData/incoming/spreadsheet.xlsx
+++ b/data-ingestion-processing/ingestionData/incoming/spreadsheet.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="132">
   <si>
     <t xml:space="preserve">Sr. No.</t>
   </si>
@@ -300,6 +300,9 @@
     <t xml:space="preserve">Remarks</t>
   </si>
   <si>
+    <t xml:space="preserve">Topic</t>
+  </si>
+  <si>
     <t xml:space="preserve">File Ingestion</t>
   </si>
   <si>
@@ -309,24 +312,45 @@
     <t xml:space="preserve">Multi-format support pending</t>
   </si>
   <si>
+    <t xml:space="preserve">Prompt injection</t>
+  </si>
+  <si>
     <t xml:space="preserve">Read file content</t>
   </si>
   <si>
+    <t xml:space="preserve">Jailbreak attempts</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chunking</t>
   </si>
   <si>
     <t xml:space="preserve">Using TokenTextSplitter</t>
   </si>
   <si>
+    <t xml:space="preserve">off-topic queries</t>
+  </si>
+  <si>
     <t xml:space="preserve">Embedding generation</t>
   </si>
   <si>
     <t xml:space="preserve">Multi-modal embeddings pending</t>
   </si>
   <si>
+    <t xml:space="preserve">Guardrails Input(Pre-Processing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regex based checks</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vector database storage</t>
   </si>
   <si>
+    <t xml:space="preserve">Guardrails Output(Post-Processing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hallucination &amp; fact-checking,Structured syntax response</t>
+  </si>
+  <si>
     <t xml:space="preserve">Metadata extraction</t>
   </si>
   <si>
@@ -348,6 +372,9 @@
     <t xml:space="preserve">Document versioning</t>
   </si>
   <si>
+    <t xml:space="preserve">file level done but chunk level pending</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAG citations</t>
   </si>
   <si>
@@ -378,10 +405,19 @@
     <t xml:space="preserve">Reranking</t>
   </si>
   <si>
+    <t xml:space="preserve">requires separate reranker model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reindexing</t>
+  </si>
+  <si>
     <t xml:space="preserve">check scope of this</t>
   </si>
   <si>
-    <t xml:space="preserve">Reindexing</t>
+    <t xml:space="preserve">Guardrails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input(Pre-Processing), Output(Post-Processing)</t>
   </si>
 </sst>
 </file>
@@ -391,7 +427,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -436,32 +472,23 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFFF860D"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -523,6 +550,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -531,23 +562,19 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -604,9 +631,9 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF860D"/>
+      <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
@@ -1710,12 +1737,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="41.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="29.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="52.95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1731,263 +1760,299 @@
       <c r="D1" s="6" t="s">
         <v>91</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>94</v>
       </c>
+      <c r="D2" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" s="7"/>
+      <c r="B3" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="G3" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>97</v>
+      <c r="B4" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>99</v>
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>93</v>
+      <c r="B6" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>103</v>
-      </c>
+      <c r="B7" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>106</v>
+      <c r="B8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="10"/>
+      <c r="B9" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>112</v>
+      <c r="B11" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>114</v>
+      <c r="B12" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>109</v>
+      <c r="B13" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>109</v>
+      <c r="B14" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
